--- a/cosmos-bc-dss/docs/COSMoS_Domain_Pattern_Inventory.xlsx
+++ b/cosmos-bc-dss/docs/COSMoS_Domain_Pattern_Inventory.xlsx
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18 BCs, all 1:1. Disposition event types.</t>
+          <t>20 BCs, all 1:1. Disposition event types.</t>
         </is>
       </c>
     </row>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O16" s="7" t="n">
         <v>4</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>30 of 93 BCs fan out. Specimen is primary axis (27 BCs), Scale secondary (9 BCs). Method is NOT a decomposition driver (0 BCs). LOINC on 135 of 142 DSSs. This is the validated pattern in Specimen_Findings.xlsx.</t>
+          <t>30 of 97 BCs fan out. Specimen is primary axis (27 BCs), Scale secondary (9 BCs). Method is NOT a decomposition driver (0 BCs). LOINC on 136 of 146 DSSs. This is the validated pattern in Specimen_Findings.xlsx.</t>
         </is>
       </c>
     </row>
@@ -2297,166 +2297,166 @@
       </c>
     </row>
     <row r="24" ht="409.6" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Respiratory System Findings</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Measurement Findings</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Measurement Findings</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>1:1.0</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>Flat PFT-dominated catalog</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>Two-sheet (shape preserved for cross-track consistency with Specimen_Findings).</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>New in COSMoS 2026-Q1. Pure flat 1:1 — zero fan-out. 111 of 135 BCs have "Pulmonary Function Test" as top-level hierarchy root; 103 carry the PFT category tag. 125 quantitative, 10 qualitative. 55 have units. No specimen, method, LOINC, location, or laterality — no decomposition axes at all. Behaviourally closest to Domain-specific Findings despite being grouped under Measurement Findings for structural-type purposes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Disease Response and Clin Classification</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Instrument Findings</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Instrument Findings</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E25" s="5" t="n">
         <v>129</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F25" s="5" t="n">
         <v>135</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>1:1.0</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H25" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="I25" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Hierarchy + Response criteria</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="5" t="inlineStr">
+      <c r="L25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>Instrument hierarchy + criteria variants</t>
         </is>
       </c>
-      <c r="Q24" s="5" t="inlineStr">
+      <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>Single-sheet with hierarchy. Criteria (RECIST/Lugano/RANO) as decomposition axis.</t>
         </is>
       </c>
-      <c r="R24" s="5" t="inlineStr">
+      <c r="R25" s="5" t="inlineStr">
         <is>
           <t>129 BCs → 135 DSSs. 4 BCs fan out by response criteria system: Overall Response, Target Response, Non-Target Response, New Lesion Indicator each have RECIST 1.1 / Lugano / RANO variants. Hierarchy depth 1-3. Mostly qualitative (132 of 135). Many parent instruments (AIMS, APACHE II, ATLAS, BPRS, etc.).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="80" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Subject Characteristics</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Domain-specific Findings</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Domain-specific Findings</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1:1.0</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>Domain-specific flat</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>Single-sheet. No decomposition.</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>2 BCs, all 1:1. Subject characteristics.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="192" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Skin Response</t>
+          <t>Subject Characteristics</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
@@ -2520,463 +2520,539 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>12 BCs, all 1:1. 3 have method. 6 quantitative, 6 qualitative. Skin response assessments.</t>
+          <t>2 BCs, all 1:1. Subject characteristics.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="409.6" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Substance Use</t>
+          <t>Skin Response</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Interventions</t>
+          <t>Domain-specific Findings</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Interventions</t>
+          <t>Domain-specific Findings</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>12</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1:4.0</t>
+          <t>1:1.0</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Context/Subtype</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Intervention subtypes</t>
+          <t>Domain-specific flat</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Single-sheet. Subtypes as rows.</t>
+          <t>Single-sheet. No decomposition.</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3 BCs → 12 DSSs. Each substance type fans out to specific substances: Alcohol → Beer/Wine/Spirits, Caffeine → Coffee/Cola/Tea, Tobacco → Cigarette/Cigar/Pipe. Study-design-driven: protocol decides which to collect.</t>
+          <t>12 BCs, all 1:1. 3 have method. 6 quantitative, 6 qualitative. Skin response assessments.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="272" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Substance Use</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Interventions</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Interventions</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1:4.0</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Context/Subtype</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Intervention subtypes</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Single-sheet. Subtypes as rows.</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>3 BCs → 12 DSSs. Each substance type fans out to specific substances: Alcohol → Beer/Wine/Spirits, Caffeine → Coffee/Cola/Tea, Tobacco → Cigarette/Cigar/Pipe. Study-design-driven: protocol decides which to collect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="365" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Tumor/Lesion Results</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Clinical Assessment Findings</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Clinical Assessment Findings</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F29" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1:2.2</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="I29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Linked records</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="2" t="n">
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="2" t="n">
+      <c r="N29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>Clinical assessment, cross-domain links</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>Single-sheet, but needs RELREC context for full value.</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>4 BCs → 9 DSSs. All 9 have method. Fan-out by method and anatomical context. 4 have units. 2 quantitative, 7 qualitative.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="365" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="30" ht="144" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>TS</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Trial Summary</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Trial Design</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Trial Design</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>1:1.0</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
+      <c r="L30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
         <is>
           <t>Trial-level parameters</t>
         </is>
       </c>
-      <c r="Q29" s="3" t="inlineStr">
+      <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>Out of scope — BC_Scope=Study, not subject-level.</t>
         </is>
       </c>
-      <c r="R29" s="3" t="inlineStr">
+      <c r="R30" s="3" t="inlineStr">
         <is>
           <t>128 BCs → 129 DSSs. Study-level metadata (SPONSOR, ACTSUB, SENDTC, etc.). Explicitly excluded from subject-level consumer files. sdtm-test-codes track also excludes TSPARMCD/TSPARM.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="144" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31" ht="395" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Tumor/Lesion Identification</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Clinical Assessment Findings</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Clinical Assessment Findings</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F31" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1:2.0</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="I31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Linked records</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="2" t="n">
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>Clinical assessment, cross-domain links</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>Single-sheet, but needs RELREC context for full value.</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>5 BCs → 10 DSSs. 6 have method. All qualitative. Tumour identification.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="395" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="32" ht="395" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>UR</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Urinary System Findings</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Specimen-based Findings</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Domain-specific Findings</t>
         </is>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E32" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F32" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>1:1.0</t>
         </is>
       </c>
-      <c r="H31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="9" t="n">
+      <c r="H32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="9" t="n">
+      <c r="L32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="P31" s="9" t="inlineStr">
+      <c r="P32" s="9" t="inlineStr">
         <is>
           <t>Flat 1:1 (misclassified as Specimen-based)</t>
         </is>
       </c>
-      <c r="Q31" s="9" t="inlineStr">
+      <c r="Q32" s="9" t="inlineStr">
         <is>
           <t>Single-sheet. No decomposition to expose.</t>
         </is>
       </c>
-      <c r="R31" s="9" t="inlineStr">
+      <c r="R32" s="9" t="inlineStr">
         <is>
           <t>10 BCs, all 1:1. Single specimen value (URINE) on 1 row, single method (MRI) on 1 row. No LOINC, no units. Behaviourally identical to Domain-specific Findings despite Specimen-based classification.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="395" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>VS</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Vital Signs</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Measurement Findings</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Measurement Findings</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>1:1.3</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
+      <c r="E33" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>1:1.1</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I33" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Location/Laterality</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="4" t="n">
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>None (flat catalog)</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Location/Laterality (residual)</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="N32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="4" t="n">
+      <c r="N33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>Location/Laterality variants</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>Single-sheet likely sufficient. Location/laterality as filter columns.</t>
-        </is>
-      </c>
-      <c r="R32" s="4" t="inlineStr">
-        <is>
-          <t>12 BCs, 4 fan out via _EXT variants adding location and laterality options. 8 BCs remain 1:1. The _EXT pattern is about where on the body, not what sample. Method on 1 DSS only. 8 have units. 0 LOINC.</t>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>Flat measurement catalog; residual _EXT variants</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>Two-sheet (shape preserved for cross-track consistency with Specimen_Findings). Location/laterality as optional columns.</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>Pre-2026-Q1: 12 BCs, 16 DSSs with _EXT location/laterality fan-out as primary pattern. After 2026-Q1 expansion: 74 BCs, 78 DSSs dominated by Body Measurements (anatomical circumferences, skinfolds, BMI/BSA, fetal measurements). Only 4 BCs still fan out (max 2:1). Top hierarchy roots: Vital Signs Measurement, Anatomical Circumference, Personal Attribute, Length, Weight. 76 quantitative, 2 qualitative. Location on 13 rows, laterality on 9. No LOINC.</t>
         </is>
       </c>
     </row>
